--- a/Documentació Projecte/Fitxa tasques de manteniment Maquina Vending.xlsx
+++ b/Documentació Projecte/Fitxa tasques de manteniment Maquina Vending.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseg\Documents\Estudios\Superior ARI 2\2n Superior\Proyecto Archivos finales\1. Documentació Projecte\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseg\Documents\Estudios\Superior ARI 2\2n Superior\Projecte CFGS Maquina Vending\Documentació Projecte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A74E185-41C9-4868-9B87-07EFE138543A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939B91F4-8DD2-4652-84C0-F149E04AACFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -575,6 +575,15 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -582,29 +591,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -920,6 +920,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -992,16 +995,16 @@
       <c r="H3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="47" t="s">
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="M3" s="45"/>
-      <c r="N3" s="46"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="40"/>
     </row>
     <row r="4" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -1034,12 +1037,12 @@
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="43"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="47"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
@@ -1054,12 +1057,12 @@
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="40"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="43"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
@@ -1074,12 +1077,12 @@
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="40"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="43"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
@@ -1094,12 +1097,12 @@
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="40"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="43"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
@@ -1114,12 +1117,12 @@
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="40"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="43"/>
     </row>
     <row r="10" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1134,12 +1137,12 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="7"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="40"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="43"/>
     </row>
     <row r="11" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
@@ -1172,12 +1175,12 @@
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="40"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="43"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
@@ -1192,12 +1195,12 @@
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="40"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="43"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
@@ -1212,12 +1215,12 @@
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
       <c r="H14" s="7"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="40"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="43"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
@@ -1232,12 +1235,12 @@
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="7"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="40"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="43"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
@@ -1252,12 +1255,12 @@
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
       <c r="H16" s="7"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="40"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="43"/>
     </row>
     <row r="17" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1272,12 +1275,12 @@
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
       <c r="H17" s="7"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="40"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="43"/>
     </row>
     <row r="18" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
@@ -1310,12 +1313,12 @@
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="43"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
@@ -1330,12 +1333,12 @@
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
       <c r="H20" s="7"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="40"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="43"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
@@ -1350,12 +1353,12 @@
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
       <c r="H21" s="7"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="40"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="43"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
@@ -1370,12 +1373,12 @@
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
       <c r="H22" s="7"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="40"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="43"/>
     </row>
     <row r="23" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -1390,12 +1393,12 @@
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="H23" s="7"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="40"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="41"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
@@ -1428,12 +1431,12 @@
       </c>
       <c r="G25" s="11"/>
       <c r="H25" s="7"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="40"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="43"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1448,12 +1451,12 @@
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="7"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="40"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="43"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
@@ -1468,12 +1471,12 @@
       </c>
       <c r="G27" s="11"/>
       <c r="H27" s="7"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="40"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="43"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
@@ -1488,12 +1491,12 @@
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="7"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="43"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
@@ -1508,12 +1511,12 @@
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="7"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="40"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="43"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="20" t="s">
@@ -1548,12 +1551,12 @@
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="7"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="38"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="40"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="41"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="43"/>
     </row>
     <row r="32" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="31" t="s">
@@ -1586,12 +1589,12 @@
         <v>3</v>
       </c>
       <c r="H33" s="7"/>
-      <c r="I33" s="38"/>
-      <c r="J33" s="39"/>
-      <c r="K33" s="40"/>
-      <c r="L33" s="38"/>
-      <c r="M33" s="39"/>
-      <c r="N33" s="40"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="43"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
@@ -1608,12 +1611,12 @@
         <v>3</v>
       </c>
       <c r="H34" s="7"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="38"/>
-      <c r="M34" s="39"/>
-      <c r="N34" s="40"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="43"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
@@ -1628,12 +1631,12 @@
         <v>3</v>
       </c>
       <c r="H35" s="7"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="38"/>
-      <c r="M35" s="39"/>
-      <c r="N35" s="40"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="42"/>
+      <c r="N35" s="43"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
@@ -1648,12 +1651,12 @@
         <v>3</v>
       </c>
       <c r="H36" s="7"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="38"/>
-      <c r="M36" s="39"/>
-      <c r="N36" s="40"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="41"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="43"/>
     </row>
     <row r="37" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
@@ -1668,12 +1671,12 @@
         <v>3</v>
       </c>
       <c r="H37" s="7"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="38"/>
-      <c r="M37" s="39"/>
-      <c r="N37" s="40"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="41"/>
+      <c r="M37" s="42"/>
+      <c r="N37" s="43"/>
     </row>
     <row r="38" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
@@ -1706,12 +1709,12 @@
       <c r="H39" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="I39" s="38"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="38"/>
-      <c r="M39" s="39"/>
-      <c r="N39" s="40"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="41"/>
+      <c r="M39" s="42"/>
+      <c r="N39" s="43"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
@@ -1726,12 +1729,12 @@
       <c r="H40" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="I40" s="38"/>
-      <c r="J40" s="39"/>
-      <c r="K40" s="40"/>
-      <c r="L40" s="38"/>
-      <c r="M40" s="39"/>
-      <c r="N40" s="40"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="41"/>
+      <c r="M40" s="42"/>
+      <c r="N40" s="43"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
@@ -1746,12 +1749,12 @@
       <c r="H41" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="I41" s="38"/>
-      <c r="J41" s="39"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="38"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="40"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="41"/>
+      <c r="M41" s="42"/>
+      <c r="N41" s="43"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
@@ -1766,12 +1769,12 @@
       <c r="H42" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="I42" s="38"/>
-      <c r="J42" s="39"/>
-      <c r="K42" s="40"/>
-      <c r="L42" s="38"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="40"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="43"/>
+      <c r="L42" s="41"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="43"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
@@ -1786,32 +1789,51 @@
       <c r="H43" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="38"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="40"/>
-      <c r="L43" s="38"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="40"/>
+      <c r="I43" s="41"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="41"/>
+      <c r="M43" s="42"/>
+      <c r="N43" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="L43:N43"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:N25"/>
     <mergeCell ref="I21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="L10:N10"/>
@@ -1828,47 +1850,28 @@
     <mergeCell ref="I15:K15"/>
     <mergeCell ref="I16:K16"/>
     <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="L43:N43"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="84" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="54" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>